--- a/material_database.xlsx
+++ b/material_database.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="90">
   <si>
     <t>名称</t>
   </si>
@@ -202,9 +202,6 @@
     <t>现金款</t>
   </si>
   <si>
-    <t>待补</t>
-  </si>
-  <si>
     <t>蛋糕盒款式</t>
   </si>
   <si>
@@ -220,7 +217,13 @@
     <t>礼物包装</t>
   </si>
   <si>
-    <t>价格规则</t>
+    <t>礼物包装-大</t>
+  </si>
+  <si>
+    <t>礼物包装-中</t>
+  </si>
+  <si>
+    <t>礼物包装-小</t>
   </si>
   <si>
     <t>现金代取费用</t>
@@ -229,37 +232,46 @@
     <t>现金包装</t>
   </si>
   <si>
-    <t>金额×0.003</t>
-  </si>
-  <si>
-    <t>基础款（肥牛卷、尖尖角花束、包裹款、折叠款）现金1w费用</t>
-  </si>
-  <si>
-    <t>298（不包现金、不加花的全部费用）</t>
-  </si>
-  <si>
-    <t>基础款（肥牛卷、尖尖角花束、包裹款、折叠款）现金5200费用</t>
-  </si>
-  <si>
-    <t>258（不包现金、不加花的全部费用）</t>
-  </si>
-  <si>
-    <t>基础款（肥牛卷、尖尖角花束、包裹款、折叠款）现金1314费用</t>
-  </si>
-  <si>
-    <t>30（现金手工费）</t>
+    <t>代取费用</t>
+  </si>
+  <si>
+    <t>比例</t>
+  </si>
+  <si>
+    <t>现金基础款1w</t>
+  </si>
+  <si>
+    <t>基础款</t>
+  </si>
+  <si>
+    <t>1万元</t>
+  </si>
+  <si>
+    <t>现金基础款5200</t>
+  </si>
+  <si>
+    <t>5200元</t>
+  </si>
+  <si>
+    <t>现金基础款1314</t>
+  </si>
+  <si>
+    <t>1314元</t>
   </si>
   <si>
     <t>蝴蝶款</t>
   </si>
   <si>
-    <t>5/只</t>
+    <t>装饰款</t>
+  </si>
+  <si>
+    <t>单只</t>
   </si>
   <si>
     <t>单只玫瑰款</t>
   </si>
   <si>
-    <t>10-20张98元</t>
+    <t>10-20张</t>
   </si>
   <si>
     <t>普通款粉色Kitty</t>
@@ -913,9 +925,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1990,7 +2008,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:5">
       <c r="A34" s="1" t="s">
         <v>0</v>
       </c>
@@ -1998,13 +2016,16 @@
         <v>1</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:5">
       <c r="A35" s="2" t="s">
         <v>41</v>
       </c>
@@ -2012,13 +2033,16 @@
         <v>42</v>
       </c>
       <c r="C35" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D35" s="2">
+      <c r="E35" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:5">
       <c r="A36" s="2" t="s">
         <v>44</v>
       </c>
@@ -2026,13 +2050,16 @@
         <v>42</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D36" s="2">
+      <c r="E36" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:5">
       <c r="A37" s="2" t="s">
         <v>44</v>
       </c>
@@ -2040,13 +2067,16 @@
         <v>42</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D37" s="2">
+      <c r="E37" s="2">
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:5">
       <c r="A38" s="2" t="s">
         <v>45</v>
       </c>
@@ -2054,13 +2084,16 @@
         <v>42</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D38" s="2">
+      <c r="E38" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:5">
       <c r="A39" s="2" t="s">
         <v>45</v>
       </c>
@@ -2068,13 +2101,16 @@
         <v>42</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D39" s="2">
+      <c r="E39" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:5">
       <c r="A40" s="2" t="s">
         <v>46</v>
       </c>
@@ -2082,13 +2118,16 @@
         <v>42</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D40" s="2">
+      <c r="E40" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:5">
       <c r="A41" s="2" t="s">
         <v>47</v>
       </c>
@@ -2096,13 +2135,16 @@
         <v>42</v>
       </c>
       <c r="C41" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D41" s="2">
+      <c r="E41" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:5">
       <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
@@ -2110,13 +2152,16 @@
         <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="E43" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="44" ht="28" spans="1:4">
+    <row r="44" ht="28" spans="1:5">
       <c r="A44" s="2" t="s">
         <v>49</v>
       </c>
@@ -2124,13 +2169,16 @@
         <v>50</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D44" s="2">
+      <c r="E44" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:5">
       <c r="A45" s="2" t="s">
         <v>52</v>
       </c>
@@ -2138,13 +2186,16 @@
         <v>50</v>
       </c>
       <c r="C45" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D45" s="2">
+      <c r="E45" s="2">
         <v>80</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" ht="28" spans="1:5">
       <c r="A46" s="2" t="s">
         <v>54</v>
       </c>
@@ -2152,41 +2203,50 @@
         <v>50</v>
       </c>
       <c r="C46" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" s="2" t="s">
-        <v>57</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C47" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="D47" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>50</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D48" s="2">
+        <v>58</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E48" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:5">
       <c r="A50" s="1" t="s">
         <v>0</v>
       </c>
@@ -2194,132 +2254,186 @@
         <v>1</v>
       </c>
       <c r="C50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="E50" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:5">
       <c r="A51" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D51" s="2">
+      <c r="E51" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:5">
       <c r="A52" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D52" s="2">
+      <c r="E52" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:5">
       <c r="A53" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C53" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D53" s="2">
+      <c r="E53" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
-      <c r="A55" s="1" t="s">
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" s="2" t="s">
+      <c r="C55" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="B56" s="4" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="57" ht="42" spans="1:4">
-      <c r="A57" s="2" t="s">
+      <c r="C56" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C57" s="2" t="s">
+      <c r="D56" s="4" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="58" ht="42" spans="1:4">
-      <c r="A58" s="2" t="s">
+      <c r="E56" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C58" s="2" t="s">
+      <c r="B57" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C57" s="4" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="59" ht="42" spans="1:4">
-      <c r="A59" s="2" t="s">
+      <c r="D57" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59" s="2" t="s">
+      <c r="E57" s="4">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="4" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" s="2" t="s">
+      <c r="B58" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C60" s="2" t="s">
+      <c r="E58" s="4">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="4" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" s="2" t="s">
+      <c r="B59" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C61" s="2" t="s">
+      <c r="E59" s="4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="4" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="63" spans="1:4">
+      <c r="B60" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E60" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E61" s="4">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63" s="1" t="s">
         <v>0</v>
       </c>
@@ -2327,121 +2441,148 @@
         <v>1</v>
       </c>
       <c r="C63" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="E63" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:5">
       <c r="A64" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C64" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D64" s="2">
+      <c r="E64" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:5">
       <c r="A65" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C65" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D65" s="2">
+      <c r="E65" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:5">
       <c r="A66" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D66" s="2">
+      <c r="E66" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:5">
       <c r="A67" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C67" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D67" s="2">
+      <c r="E67" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:5">
       <c r="A68" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="C68" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D68" s="2">
+      <c r="E68" s="2">
         <v>45</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:5">
       <c r="A69" s="2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D69" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D69" s="2">
+      <c r="E69" s="2">
         <v>35</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:5">
       <c r="A70" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D70" s="2">
+        <v>87</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E70" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:5">
       <c r="A71" s="2" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D71" s="2">
+        <v>89</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E71" s="2">
         <v>50</v>
       </c>
     </row>
